--- a/线下结算返利统计.xlsx
+++ b/线下结算返利统计.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\小芹\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A29A41-D29D-4FE6-BA31-DF8C2369B4A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="11460"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,53 +20,67 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
+<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="ID_800DBF35B51943F4968801311D3FC4AA"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12048490" y="6299200"/>
+          <a:ext cx="4095750" cy="3733800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+</etc:cellImages>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="49">
+  <si>
+    <t>厂家/集团</t>
+  </si>
   <si>
     <t>对方方主体</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>返利（支付）标准</t>
+  </si>
+  <si>
+    <t>合同到期日</t>
   </si>
   <si>
     <t>理想汽车</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>江苏心电互动汽车销售服务有限公司</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>长春承信二手车经销有限公司</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一汽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>合同到期日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>未有相关信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>长久集团</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>厂家/集团</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>广西长久汽车投资有限公司</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>合同价＜5k, 300元/台
@@ -80,97 +88,190 @@
 1W≤合同价＜5W, 500元/台
 5W≤合同价＜20W, 500元/台
 20W≤合同价, 500元/台</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未有相关信息</t>
+  </si>
+  <si>
+    <t>零跑</t>
+  </si>
+  <si>
+    <t>浙江零跑汽车销售服务有限公司</t>
+  </si>
+  <si>
+    <t>合同价≤5k, 0元/台
+5K＜合同价≤10W, 700元/台
+10W＜合同价, 1000元/台</t>
+  </si>
+  <si>
+    <t>长城</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">常有(天津)信息技术有限公司
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>厂家接口推送的，聚合拍平台，常有好车</t>
+    </r>
+  </si>
+  <si>
+    <t>聚合拍平台推送到车唯拍成交的车辆：
+成交车价＜1W, 50元/台
+1W≤成交车价＜3W, 100元/台
+3W≤成交车价＜5W, 150元/台
+5W≤成交车价＜10W, 200元/台
+10W≤成交车价, 300元/台</t>
+  </si>
+  <si>
+    <t>2027年8月14日
+在本协议有效期届满的一个月前，甲乙双方均未书面提出要终
+止本协议的，本协议应视为自动延期一年，以后类推，延期以两次为限。</t>
+  </si>
+  <si>
+    <t>一汽</t>
+  </si>
+  <si>
+    <t>长春承信二手车经销有限公司
+一汽红旗：厂家接口推送的，聚合拍平台，承信优车
+一汽大众：厂家接口推送的，聚合拍平台，承信优车</t>
+  </si>
+  <si>
+    <t>聚合拍平台推送的成交车辆：
+非拆解车辆：200元/辆（非报废）
+拆解车辆：100元/辆（报废）</t>
   </si>
   <si>
     <t>2026年7月18日
 合同期间届满前1个月，如双方未提出更改协议，则该协议自动顺延一年</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>长久集团</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">广西长久汽车投资有限公司
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>一家店如果又是长久集团，又是厂家推送的，可能存在叠加返利(eg.佛山市世锦汽车销售服务有限公司)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">按年度，超额累进制：
+成交台数≤2500, 200元/台
+2500＜成交台数≤3500, 300元/台
+3500＜成交台数, 400元/台
+不适用于报废车
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>不适用于长久集团二手车中心所拍中的车辆（账号列表丽君提供）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2026年7月31日
+协议期满双方可就合作事宜重新商议，如未签订新协议且未就本协议提出异议，视为双方同意本协议自动延期。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>成交台数是按照合同年度，非自然年度计算</t>
+    </r>
   </si>
   <si>
     <t>昊城集团</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>广州延生二手车服务有限公司</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2028年8月31日
-协议期满双方可就合作事宜重新商议，如未签订新协议且未就本协议提出异议，视为双方同意本协议自动延期。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>非报废车：
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">广州延生二手车服务有限公司
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- 精诚拍接口推送？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">非报废车：
 按年度，超额累进制：
 成交台数≤1000, 150元/台
 1000＜成交台数≤2000, 200元/台
 2000＜成交台数, 300元/台
 报废车：
 150元/台
-不适用于昊城二手车拍中的昊城门店置换车</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>按年度，超额累进制：
-成交台数≤2500, 200元/台
-2500＜成交台数≤3500, 300元/台
-3500＜成交台数, 400元/台
-不适用于报废车
-不适用于长久集团二手车中心所拍中的车辆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026年7月31日
-协议期满双方可就合作事宜重新商议，如未签订新协议且未就本协议提出异议，视为双方同意本协议自动延期。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>聚合拍平台推送的成交车辆：
-非拆解车辆：200元/辆
-拆解车辆：100元/辆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>长城</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>常有(天津)信息技术有限公司</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2027年8月14日
-在本协议有效期届满的一个月前，甲乙双方均未书面提出要终
-止本协议的，本协议应视为自动延期一年，以后类推，延期以两次为限。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>零跑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>浙江零跑汽车销售服务有限公司</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>合同价≤5k, 0元/台
-5K＜合同价≤10W, 700元/台
-10W＜合同价, 1000元/台</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>聚合拍平台推送到车唯拍成交的车辆：
-成交车价＜1W, 50元/台
-1W≤成交车价＜3W, 100元/台
-3W≤成交车价＜5W, 150元/台
-5W≤成交车价＜10W, 200元/台
-10W≤成交车价, 300元/台</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>不适用于昊城二手车拍中的昊城门店置换车
+门店账号需提供</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2028年8月31日
+协议期满双方可就合作事宜重新商议，如未签订新协议且未就本协议提出异议，视为双方同意本协议自动延期。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>成交台数是按照合同年度，非自然年度计算</t>
+    </r>
   </si>
   <si>
     <t>利泰集团</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>佛山市利泰二手车交易有限公司南海分公司</t>
   </si>
   <si>
     <t>每月成交台数≤50：
@@ -179,59 +280,91 @@
 50＜每月成交台数：
 起拍车价＜1W, 200元/台
 1W≤起拍车价, 400元/台</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>佛山市利泰二手车交易有限公司南海分公司</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴伟；黄秀敏</t>
+  </si>
+  <si>
+    <t>桂林长久鑫广达二手车销售有限公司</t>
+  </si>
+  <si>
+    <t>固定：2500元/月</t>
+  </si>
+  <si>
+    <t>2026年7月31日</t>
+  </si>
+  <si>
+    <t>黄zuan. 次月1次，平均至每台车上；</t>
+  </si>
+  <si>
+    <t>广西长久二手车销售有限公司</t>
+  </si>
+  <si>
+    <t>固定：4500元/月</t>
+  </si>
+  <si>
+    <t>其他</t>
   </si>
   <si>
     <t>深圳深汕特别合作区蓝骏汽车维修经营部（个体工商户）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>订单中“其他费用”金额
 （没有在平台清分，线下申请支付）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>返利（支付）标准</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>2028年12月31日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>桂林长久鑫广达二手车销售有限公司</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026年7月31日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>固定：2500元/月</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>广西长久二手车销售有限公司</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>固定：4500元/月</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>其他</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吉利</t>
+  </si>
+  <si>
+    <t>吉利厂家接口推送过来的成交订单清分后</t>
+  </si>
+  <si>
+    <t>100元/台</t>
+  </si>
+  <si>
+    <t>广汽本田、奇瑞汽车(未接入)、捷途汽车、爱咖汽车品牌</t>
+  </si>
+  <si>
+    <r>
+      <t>北京智享乐通科技有限公司
+接口</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：360</t>
+    </r>
+  </si>
+  <si>
+    <t>奔腾（未接入）</t>
+  </si>
+  <si>
+    <t>北京智享乐通科技有限公司（360数据平台公司）：
+奔腾拍接口推送</t>
+  </si>
+  <si>
+    <t>150元/台</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -240,7 +373,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -249,28 +384,169 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -279,12 +555,204 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -294,31 +762,282 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -326,33 +1045,107 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="31" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="31" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="31" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="31" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="31" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -602,200 +1395,262 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:D12"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A2:E19"/>
+  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="24" customHeight="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="12.875" customWidth="1"/>
-    <col min="2" max="2" width="48.5" customWidth="1"/>
-    <col min="3" max="3" width="45.5" customWidth="1"/>
-    <col min="4" max="4" width="52.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="25.6153846153846" customWidth="1"/>
+    <col min="2" max="2" width="53.2788461538462" customWidth="1"/>
+    <col min="3" max="3" width="50.125" customWidth="1"/>
+    <col min="4" max="4" width="59.1730769230769" style="2" customWidth="1"/>
+    <col min="5" max="5" width="44.3653846153846" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="7" t="s">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:4">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" ht="90" customHeight="1" spans="1:4">
+      <c r="A3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" ht="83" customHeight="1" spans="1:4">
+      <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="B4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" ht="150" customHeight="1" spans="1:4">
+      <c r="A5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" ht="125" customHeight="1" spans="1:4">
+      <c r="A6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" ht="172" customHeight="1" spans="1:5">
+      <c r="A7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="str">
+        <f>_xlfn.DISPIMG("ID_800DBF35B51943F4968801311D3FC4AA",1)</f>
+        <v>=DISPIMG("ID_800DBF35B51943F4968801311D3FC4AA",1)</v>
+      </c>
+    </row>
+    <row r="8" ht="190" customHeight="1" spans="1:4">
+      <c r="A8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" ht="138" customHeight="1" spans="1:5">
+      <c r="A9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" ht="32.25" customHeight="1" spans="1:5">
+      <c r="A10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="72.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="90.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="2" t="s">
+      <c r="C10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" ht="32.25" customHeight="1" spans="1:5">
+      <c r="A11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="120" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="159" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="112.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="6" t="s">
+      <c r="E11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="3" t="s">
+    <row r="12" ht="75.75" customHeight="1" spans="1:4">
+      <c r="A12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="75.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="2" t="s">
+      <c r="B12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>32</v>
-      </c>
+      <c r="C12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" ht="25" customHeight="1" spans="1:4">
+      <c r="A13" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="16"/>
+    </row>
+    <row r="14" ht="45" customHeight="1" spans="1:3">
+      <c r="A14" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" ht="43" customHeight="1" spans="1:3">
+      <c r="A15" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="3:3">
+      <c r="C16" s="20"/>
+    </row>
+    <row r="17" ht="28" customHeight="1" spans="3:3">
+      <c r="C17" s="20"/>
+    </row>
+    <row r="18" ht="28" customHeight="1" spans="3:3">
+      <c r="C18" s="20"/>
+    </row>
+    <row r="19" ht="200" customHeight="1" spans="3:3">
+      <c r="C19" s="20"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>